--- a/老余裸K圖表_20260615/老余裸K_賺賠比精選_20260615.xlsx
+++ b/老余裸K圖表_20260615/老余裸K_賺賠比精選_20260615.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -547,33 +547,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4577.TWO</t>
+          <t>2208.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>台船</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1 : 17.07</t>
+          <t>1 : 5.71</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>91</v>
+        <v>17.9</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>85.2</v>
+        <v>17.2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>190</v>
+        <v>21.9</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>753</v>
+        <v>2674</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -584,33 +584,33 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2630.TW</t>
+          <t>1301.TW</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>1 : 11.21</t>
+          <t>1 : 5.14</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>39.35</v>
+        <v>45.25</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>38.15</v>
+        <v>43.1</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>52.8</v>
+        <v>56.3</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>867</v>
+        <v>21404</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,33 +621,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3339.TWO</t>
+          <t>8033.TW</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1 : 6.44</t>
+          <t>1 : 4.97</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>45</v>
+        <v>129.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>40.7</v>
+        <v>123</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>72.7</v>
+        <v>161.78</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3604</v>
+        <v>1700</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -658,33 +658,33 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>3543.TW</t>
+          <t>4714.TWO</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>1 : 5.65</t>
+          <t>1 : 4.87</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>32.55</v>
+        <v>13.55</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>30.1</v>
+        <v>12.75</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>46.4</v>
+        <v>17.45</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>2.45</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>506</v>
+        <v>680</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -695,33 +695,33 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1569.TWO</t>
+          <t>6919.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.57</t>
+          <t>1 : 4.61</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>49.85</v>
+        <v>92.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>46.05</v>
+        <v>87</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>67.2</v>
+        <v>119</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>942</v>
+        <v>2813</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -732,33 +732,33 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>6426.TW</t>
+          <t>1584.TWO</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>精剛</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1 : 4.36</t>
+          <t>1 : 3.93</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>209</v>
+        <v>19.65</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>189.5</v>
+        <v>18.95</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>294</v>
+        <v>22.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>19.5</v>
+        <v>0.7</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>1295</v>
+        <v>689</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -769,33 +769,33 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6643.TWO</t>
+          <t>8011.TW</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.27</t>
+          <t>1 : 3.8</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>493</v>
+        <v>18.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>437.5</v>
+        <v>17.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>730</v>
+        <v>22.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>55.5</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>511</v>
+        <v>1164</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -806,33 +806,33 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>6909.TW</t>
+          <t>8213.TW</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>1 : 4.21</t>
+          <t>1 : 3.23</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>47.65</v>
+        <v>36.05</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>42.3</v>
+        <v>33.65</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>70.16</v>
+        <v>43.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>5.35</v>
+        <v>2.4</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -843,33 +843,33 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>5452.TWO</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1 : 3.79</t>
+          <t>1 : 2.65</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>26</v>
+        <v>32.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>24.05</v>
+        <v>30.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>33.4</v>
+        <v>37.5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>4392</v>
+        <v>1532</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -880,33 +880,33 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2419.TW</t>
+          <t>5521.TW</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>仲琦</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>1 : 3.65</t>
+          <t>1 : 2.39</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>29.75</v>
+        <v>10.55</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>27.35</v>
+        <v>9.65</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>38.5</v>
+        <v>12.7</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>2227</v>
+        <v>7184</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -917,33 +917,33 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>6683.TWO</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1 : 3.38</t>
+          <t>1 : 2.31</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1585</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1295</v>
+        <v>56.7</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2565</v>
+        <v>81.2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>290</v>
+        <v>7.4</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1453</v>
+        <v>43895</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -954,33 +954,33 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>3031.TW</t>
+          <t>4114.TWO</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>佰鴻</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>1 : 3.27</t>
+          <t>1 : 2.27</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>28.75</v>
+        <v>30.5</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>26.75</v>
+        <v>29.75</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>35.3</v>
+        <v>32.2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>705</v>
+        <v>848</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -991,257 +991,35 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>6588.TWO</t>
+          <t>5469.TW</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1 : 3.15</t>
+          <t>1 : 2.12</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>112</v>
+        <v>83.7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>94.7</v>
+        <v>76</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>166.5</v>
+        <v>100</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>17.3</v>
+        <v>7.7</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>504</v>
+        <v>3015</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>3081.TWO</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.13</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>2335</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>3305</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>310</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>2066</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>6584.TWO</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1 : 2.84</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>625</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>544</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>855</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>593</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>3689.TWO</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>湧德</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>1 : 2.79</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6919.TW</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>康霈*</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>1 : 2.76</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>4329</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>3289.TWO</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>宜特</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>1 : 2.5</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>169</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>149</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>219</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>1947</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>1301.TW</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>1 : 2.18</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>36123</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1262,12 +1040,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
